--- a/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.5_Compliance_Dashboard_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.5_Compliance_Dashboard_20260208.xlsx
@@ -2031,7 +2031,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 Compliant Methods (%)</t>
+          <t>NIST SP 800-88 Rev. 2 Compliant Methods (%)</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
